--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-19).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-19).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-172</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 1.691.295,97</t>
-  </si>
-  <si>
-    <t>R$ 9.292,84
-R$ 9.436,34</t>
-  </si>
-  <si>
-    <t>(1.4%)
-0.1%</t>
-  </si>
-  <si>
-    <t>96.9</t>
-  </si>
-  <si>
-    <t>(6.5%)</t>
-  </si>
-  <si>
-    <t>26.2%</t>
-  </si>
-  <si>
-    <t>(18.3%)</t>
+175</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 1.719.944,24</t>
+  </si>
+  <si>
+    <t>R$ 9.297,00
+R$ 9.438,28</t>
+  </si>
+  <si>
+    <t>(1.3%)
+0.2%</t>
+  </si>
+  <si>
+    <t>97.1</t>
+  </si>
+  <si>
+    <t>(6.2%)</t>
+  </si>
+  <si>
+    <t>29.6%</t>
+  </si>
+  <si>
+    <t>(14.7%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,10 +950,10 @@
     <t>29.7</t>
   </si>
   <si>
-    <t>61.3%</t>
-  </si>
-  <si>
-    <t>15.9%</t>
+    <t>61.0%</t>
+  </si>
+  <si>
+    <t>15.8%</t>
   </si>
   <si>
     <t>6.5</t>
@@ -962,19 +962,19 @@
     <t>7.7</t>
   </si>
   <si>
-    <t>14.6</t>
+    <t>14.5</t>
   </si>
   <si>
     <t>21.2</t>
   </si>
   <si>
-    <t>62.2%</t>
-  </si>
-  <si>
-    <t>-R$ 51.307,06</t>
-  </si>
-  <si>
-    <t>2.94</t>
+    <t>62.1%</t>
+  </si>
+  <si>
+    <t>-R$ 52.531,59</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2213,10 +2213,10 @@
         <v>0.20720720720720731</v>
       </c>
       <c r="T7" s="6">
-        <v>0.34242735832877602</v>
+        <v>0.34828049912374387</v>
       </c>
       <c r="U7" s="6">
-        <v>0.010999388350393524</v>
+        <v>0.016852529145361363</v>
       </c>
       <c r="V7" s="6">
         <v>0.026984493836029331</v>
@@ -5841,10 +5841,10 @@
         <v>0.36956521739130443</v>
       </c>
       <c r="T35" s="6">
-        <v>2.4576651058367882</v>
+        <v>10.889540158945255</v>
       </c>
       <c r="U35" s="6">
-        <v>0.20744931775186828</v>
+        <v>8.6393243708603347</v>
       </c>
       <c r="V35" s="6">
         <v>0.053410569814712941</v>
@@ -8720,7 +8720,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8756,25 +8756,59 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>12444.1</v>
+      </c>
+      <c r="P58" s="5">
+        <v>12444.1</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.25737352100152577</v>
+      </c>
+      <c r="R58" s="7">
+        <v>137</v>
+      </c>
+      <c r="S58" s="6">
+        <v>0.15126050420168058</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.38546431642304385</v>
+      </c>
+      <c r="U58" s="6">
+        <v>0.026556078784323492</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.0099695437998730315</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.001053350583810802</v>
+      </c>
+      <c r="X58" s="8">
+        <v>30.423174285714286</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.31428571428571428</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>6.6127737226277379</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>8.0538095238095231</v>
+      </c>
       <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>22.408254285714285</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.43809523809523809</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-511.5</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -16871,7 +16905,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -23000,7 +23034,7 @@
         <v>19890</v>
       </c>
       <c r="B172" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C172" s="4">
         <v>44</v>
@@ -23036,25 +23070,61 @@
       <c t="s" r="N172" s="4">
         <v>52</v>
       </c>
-      <c r="O172" s="5"/>
-      <c r="P172" s="5"/>
-      <c r="Q172" s="6"/>
-      <c r="R172" s="7"/>
-      <c r="S172" s="6"/>
-      <c r="T172" s="6"/>
-      <c r="U172" s="6"/>
-      <c r="V172" s="6"/>
-      <c r="W172" s="6"/>
-      <c r="X172" s="8"/>
-      <c r="Y172" s="6"/>
-      <c r="Z172" s="6"/>
-      <c r="AA172" s="8"/>
-      <c r="AB172" s="8"/>
-      <c r="AC172" s="8"/>
-      <c r="AD172" s="8"/>
-      <c r="AE172" s="6"/>
+      <c r="O172" s="5">
+        <v>5644.6700000000001</v>
+      </c>
+      <c r="P172" s="5">
+        <v>5644.6700000000001</v>
+      </c>
+      <c r="Q172" s="6">
+        <v>-0.25718252401631791</v>
+      </c>
+      <c r="R172" s="7">
+        <v>63</v>
+      </c>
+      <c r="S172" s="6">
+        <v>-0.086956521739130488</v>
+      </c>
+      <c r="T172" s="6">
+        <v>0.26005612374151194</v>
+      </c>
+      <c r="U172" s="6">
+        <v>0.0036071196367546731</v>
+      </c>
+      <c r="V172" s="6">
+        <v>0.052614767559485319</v>
+      </c>
+      <c r="W172" s="6">
+        <v>0.02326495614446903</v>
+      </c>
+      <c r="X172" s="8">
+        <v>19.207232075471698</v>
+      </c>
+      <c r="Y172" s="6">
+        <v>0.96226415094339623</v>
+      </c>
+      <c r="Z172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA172" s="8">
+        <v>4.4048387096774198</v>
+      </c>
+      <c r="AB172" s="8">
+        <v>3.3389943396226416</v>
+      </c>
+      <c r="AC172" s="8">
+        <v>7.7833319999999997</v>
+      </c>
+      <c r="AD172" s="8">
+        <v>14.746226415094339</v>
+      </c>
+      <c r="AE172" s="6">
+        <v>0.98113207547169812</v>
+      </c>
       <c r="AF172" s="9"/>
-      <c r="AG172" s="5"/>
+      <c r="AG172" s="5">
+        <v>-112.2</v>
+      </c>
       <c r="AH172" s="10">
         <v>1</v>
       </c>
@@ -25931,7 +26001,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25967,25 +26037,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>10559.5</v>
+      </c>
+      <c r="P195" s="5">
+        <v>10559.5</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>0.19906568374961964</v>
+      </c>
+      <c r="R195" s="7">
+        <v>121</v>
+      </c>
+      <c r="S195" s="6">
+        <v>0.17475728155339798</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.31649214451441826</v>
+      </c>
+      <c r="U195" s="6">
+        <v>-0.003782489701216914</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.013797007434064115</v>
+      </c>
+      <c r="W195" s="6">
+        <v>-0.001484966144230314</v>
+      </c>
+      <c r="X195" s="8">
+        <v>29.821580769230767</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0.10256410256410256</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>5.6540178571428568</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>9.6119653846153845</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>22.17970128205128</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.53846153846153844</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-600.83000000000004</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-19).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-19).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-175</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 1.719.944,24</t>
-  </si>
-  <si>
-    <t>R$ 9.297,00
-R$ 9.438,28</t>
-  </si>
-  <si>
-    <t>(1.3%)
-0.2%</t>
-  </si>
-  <si>
-    <t>97.1</t>
-  </si>
-  <si>
-    <t>(6.2%)</t>
-  </si>
-  <si>
-    <t>29.6%</t>
-  </si>
-  <si>
-    <t>(14.7%)</t>
+176</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.727.479,52</t>
+  </si>
+  <si>
+    <t>R$ 9.287,52
+R$ 9.427,46</t>
+  </si>
+  <si>
+    <t>(1.4%)
+0.1%</t>
+  </si>
+  <si>
+    <t>97.0</t>
+  </si>
+  <si>
+    <t>(6.3%)</t>
+  </si>
+  <si>
+    <t>29.7%</t>
+  </si>
+  <si>
+    <t>(14.6%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,10 +950,10 @@
     <t>29.7</t>
   </si>
   <si>
-    <t>61.0%</t>
-  </si>
-  <si>
-    <t>15.8%</t>
+    <t>60.8%</t>
+  </si>
+  <si>
+    <t>15.9%</t>
   </si>
   <si>
     <t>6.5</t>
@@ -962,7 +962,7 @@
     <t>7.7</t>
   </si>
   <si>
-    <t>14.5</t>
+    <t>14.6</t>
   </si>
   <si>
     <t>21.2</t>
@@ -971,7 +971,7 @@
     <t>62.1%</t>
   </si>
   <si>
-    <t>-R$ 52.531,59</t>
+    <t>-R$ 52.573,49</t>
   </si>
   <si>
     <t>2.95</t>
@@ -3025,7 +3025,9 @@
       <c r="AB13" s="8">
         <v>9.4508956989247324</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>20.203942000000001</v>
+      </c>
       <c r="AD13" s="8">
         <v>27.147132258064516</v>
       </c>
@@ -5708,10 +5710,10 @@
         <v>0.0064102564102563875</v>
       </c>
       <c r="T34" s="6">
-        <v>0.29498310995976884</v>
+        <v>0.34512214882135112</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.012726207470929098</v>
+        <v>0.037412831390653212</v>
       </c>
       <c r="V34" s="6">
         <v>0.05726315829262546</v>
@@ -8798,7 +8800,9 @@
       <c r="AB58" s="8">
         <v>8.0538095238095231</v>
       </c>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>15.478569999999999</v>
+      </c>
       <c r="AD58" s="8">
         <v>22.408254285714285</v>
       </c>
@@ -10982,7 +10986,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -11016,25 +11020,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>7535.2799999999997</v>
+      </c>
+      <c r="P76" s="5">
+        <v>7535.2799999999997</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.23056940853561403</v>
+      </c>
+      <c r="R76" s="7">
+        <v>87</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.21621621621621623</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0.37659737926128828</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-0.048420669172213902</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.02524544542472211</v>
+      </c>
+      <c r="W76" s="6">
+        <v>0.0028560982471786053</v>
+      </c>
+      <c r="X76" s="8">
+        <v>31.547115384615385</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.17307692307692307</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>6.3384123809523816</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>9.3939723404255329</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>16.012542</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>23.591667307692305</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.57692307692307687</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-41.899999999999999</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -24025,7 +24065,9 @@
       <c r="AB179" s="8">
         <v>1.9197745762711864</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>6.1677960000000001</v>
+      </c>
       <c r="AD179" s="8">
         <v>13.120622033898306</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-19).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-19).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-176</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 1.727.479,52</t>
-  </si>
-  <si>
-    <t>R$ 9.287,52
-R$ 9.427,46</t>
+182</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 1.784.409,02</t>
+  </si>
+  <si>
+    <t>R$ 9.293,80
+R$ 9.429,47</t>
   </si>
   <si>
     <t>(1.4%)
-0.1%</t>
-  </si>
-  <si>
-    <t>97.0</t>
-  </si>
-  <si>
-    <t>(6.3%)</t>
-  </si>
-  <si>
-    <t>29.7%</t>
-  </si>
-  <si>
-    <t>(14.6%)</t>
+0.0%</t>
+  </si>
+  <si>
+    <t>96.9</t>
+  </si>
+  <si>
+    <t>(6.2%)</t>
+  </si>
+  <si>
+    <t>29.5%</t>
+  </si>
+  <si>
+    <t>(14.4%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -947,22 +947,22 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>29.7</t>
-  </si>
-  <si>
-    <t>60.8%</t>
-  </si>
-  <si>
-    <t>15.9%</t>
-  </si>
-  <si>
-    <t>6.5</t>
+    <t>29.6</t>
+  </si>
+  <si>
+    <t>61.3%</t>
+  </si>
+  <si>
+    <t>15.7%</t>
+  </si>
+  <si>
+    <t>6.4</t>
   </si>
   <si>
     <t>7.7</t>
   </si>
   <si>
-    <t>14.6</t>
+    <t>14.5</t>
   </si>
   <si>
     <t>21.2</t>
@@ -971,10 +971,10 @@
     <t>62.1%</t>
   </si>
   <si>
-    <t>-R$ 52.573,49</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>-R$ 52.951,73</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>19175.549999999999</v>
+      </c>
+      <c r="P6" s="5">
+        <v>19175.549999999999</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.3836480937231439</v>
+      </c>
+      <c r="R6" s="7">
+        <v>174</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.24285714285714288</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.3211330522462198</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0.0018306072055299587</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.021527606770079605</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0024679187819906081</v>
+      </c>
+      <c r="X6" s="8">
+        <v>22.443884892086331</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.94244604316546765</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0.014388489208633094</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>7.0841954022988514</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.2324817518248179</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>9.2197709999999997</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>16.12338129496403</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.87050359712230219</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>-74.900000000000006</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -4388,7 +4424,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4424,25 +4460,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>11835.200000000001</v>
+      </c>
+      <c r="P24" s="5">
+        <v>11835.200000000001</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0.11752986166847657</v>
+      </c>
+      <c r="R24" s="7">
+        <v>132</v>
+      </c>
+      <c r="S24" s="6">
+        <v>0</v>
+      </c>
+      <c r="T24" s="6">
+        <v>-0.0064492361768284439</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.34027460456941999</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.013971373529809383</v>
+      </c>
+      <c r="W24" s="6">
+        <v>-0.0014605583344599162</v>
+      </c>
+      <c r="X24" s="8">
+        <v>30.896067415730336</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.4606741573033708</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.1348314606741573</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>5.2045217054263562</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>9.5113636363636367</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>21.506179775280899</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.42696629213483145</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-303.33999999999997</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5924,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5960,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>8344.25</v>
+      </c>
+      <c r="P36" s="5">
+        <v>8344.25</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.69883442764798698</v>
+      </c>
+      <c r="R36" s="7">
+        <v>77</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.63829787234042556</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.29200517721784458</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.0007293405638613416</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.053525781226593162</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.02487491386283968</v>
+      </c>
+      <c r="X36" s="8">
+        <v>30.569230769230767</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>6.6346486842105259</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>7.325162745098039</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>14.527727000000001</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>21.263461538461538</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.59615384615384615</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7845,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7881,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>1551.28</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1551.28</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>0.21522239804471455</v>
+      </c>
+      <c r="R51" s="7">
+        <v>12</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.19999999999999996</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.3071205713991027</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.017235766592749214</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.073760056211644581</v>
+      </c>
+      <c r="X51" s="8">
+        <v>30.900000000000002</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>5.2902750000000003</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>14.983333333333334</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>20.614284999999999</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>25.145242857142854</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12604,7 +12746,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12643,7 +12785,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12677,25 +12819,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>9518.8299999999999</v>
+      </c>
+      <c r="P89" s="5">
+        <v>9518.8299999999999</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.34578892639152059</v>
+      </c>
+      <c r="R89" s="7">
+        <v>89</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.26446280991735538</v>
+      </c>
+      <c r="T89" s="6">
+        <v>0.2956644461556725</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.032650063085484245</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.019806268207332205</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0064737472987751645</v>
+      </c>
+      <c r="X89" s="8">
+        <v>26.579999999999998</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.88571428571428568</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>3.8782054945054942</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>5.9607852941176471</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>17.946191428571428</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.74285714285714288</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16683,7 +16859,7 @@
         <v>-70.900000000000006</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -18646,7 +18822,7 @@
         <v>-257.93000000000001</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20924,7 +21100,7 @@
         <v>14.6</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -21318,7 +21494,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21354,25 +21530,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>6504.3900000000003</v>
+      </c>
+      <c r="P158" s="5">
+        <v>6504.3900000000003</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.48433107384944696</v>
+      </c>
+      <c r="R158" s="7">
+        <v>67</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.43697478991596639</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.31143716782050279</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.0095856490770079884</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.02853096139684121</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.004351906942849368</v>
+      </c>
+      <c r="X158" s="8">
+        <v>33.431481481481484</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.20370370370370369</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>5.8121212121212125</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>6.9981481481481476</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>13.140739999999999</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>20.083333333333332</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.37037037037037035</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -26121,7 +26333,9 @@
       <c r="AB195" s="8">
         <v>9.6119653846153845</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>15.256409</v>
+      </c>
       <c r="AD195" s="8">
         <v>22.17970128205128</v>
       </c>
